--- a/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week04_21Sep.xlsx
+++ b/Planning/LAUNCH/Progress_Tees_Valley_Weekly_Plan_Week04_21Sep.xlsx
@@ -1170,7 +1170,7 @@
     <row r="8" ht="33.75" customHeight="1" s="49">
       <c r="A8" s="57" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: International Day of Peace (Mon 21 Sep) — whole-school reflection + calm tutor-time minute.  European Day of Languages Sat 26 Sep — language-taster starter Fri.  EVIDENCE: assembly print + EFL: community → log in the SMSC Evidence Tracker.</t>
+          <t>SMSC/BV this week: International Day of Peace (Mon 21 Sep) — whole-school reflection + calm tutor-time minute.  European Day of Languages Sat 26 Sep — language-taster starter Fri.  EVIDENCE: assembly print + evidence platform: community → log in the SMSC Evidence Tracker.</t>
         </is>
       </c>
       <c r="B8" s="58" t="n"/>
@@ -1485,7 +1485,7 @@
       <c r="I13" s="69" t="inlineStr">
         <is>
           <t>TA runs the clinic 1:1; teacher drives the algorithm demo with live predictions from the class; photograph walls and checklists as evidence.
-LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to EFL, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
+LOOP [Feedback Policy]: Voice = recorded micro-interview / script-flip / portfolio piece [VF] → Audience: listen fully, name one strength + one [NS] before tagging; then [R] → EVIDENCE: recording/portfolio to evidence platform, same day [E: PfA/careers/transition — weekly PfA minimum].</t>
         </is>
       </c>
       <c r="J13" s="69" t="inlineStr">
